--- a/report-data/Bilan_Chinois_Exploitable_Corrige.xlsx
+++ b/report-data/Bilan_Chinois_Exploitable_Corrige.xlsx
@@ -29,10 +29,10 @@
     <t xml:space="preserve">Bilans santé total</t>
   </si>
   <si>
-    <t xml:space="preserve">Bilans de santé VIP chinois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilans de santé VIP ivoiriens</t>
+    <t xml:space="preserve">Bilans santé VIP chinois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilans santé VIP ivoiriens</t>
   </si>
   <si>
     <t xml:space="preserve">Hospitalisations entrées</t>
@@ -349,8 +349,8 @@
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Consultations total"/>
     <tableColumn id="3" name="Bilans santé total"/>
-    <tableColumn id="4" name="Bilans de santé VIP chinois"/>
-    <tableColumn id="5" name="Bilans de santé VIP ivoiriens"/>
+    <tableColumn id="4" name="Bilans santé VIP chinois"/>
+    <tableColumn id="5" name="Bilans santé VIP ivoiriens"/>
     <tableColumn id="6" name="Hospitalisations entrées"/>
     <tableColumn id="7" name="Hospitalisations sorties"/>
     <tableColumn id="8" name="Patients hospitalisés"/>
